--- a/Mechanical/Relays/Power/Database/Mechanical_Relays_Power_GOST.xlsx
+++ b/Mechanical/Relays/Power/Database/Mechanical_Relays_Power_GOST.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr showInkAnnotation="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,22 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Electronics\Mechanical\Relays\Power\Database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6F4A54B7-AC3E-482B-BF6B-D8A95D5CA1BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D14BC066-0228-4942-A69B-861F7266F4AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11235"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="List" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="144525"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -160,9 +153,6 @@
     <t>HF41F-Z</t>
   </si>
   <si>
-    <t>..\Footprints\Mechanical_Relays_Power_TH.PcbLib</t>
-  </si>
-  <si>
     <t>HF41F-Z8</t>
   </si>
   <si>
@@ -257,12 +247,15 @@
   </si>
   <si>
     <t>8069630191</t>
+  </si>
+  <si>
+    <t>..\Footprints\Mechanical_Relays_Power_THT.PcbLib</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -594,7 +587,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AK3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -642,40 +635,40 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H1" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="J1" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="K1" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="L1" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="M1" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="N1" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="P1" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="P1" s="2" t="s">
-        <v>56</v>
-      </c>
       <c r="Q1" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R1" s="2" t="s">
         <v>5</v>
@@ -755,34 +748,34 @@
         <v>28</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="O2" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="P2" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R2" s="1" t="s">
         <v>25</v>
@@ -803,16 +796,16 @@
         <v>24</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Z2" s="1" t="s">
         <v>35</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AB2" s="3" t="s">
         <v>37</v>
@@ -830,21 +823,21 @@
         <v>41</v>
       </c>
       <c r="AG2" s="1" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="AH2" s="1" t="s">
         <v>23</v>
       </c>
       <c r="AI2" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AJ2" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="AJ2" s="1" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>29</v>
@@ -853,40 +846,40 @@
         <v>30</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="O3" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="P3" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R3" s="1" t="s">
         <v>25</v>
@@ -907,16 +900,16 @@
         <v>24</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Z3" s="1" t="s">
         <v>35</v>
       </c>
       <c r="AA3" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AB3" s="3" t="s">
         <v>37</v>
@@ -931,28 +924,28 @@
         <v>40</v>
       </c>
       <c r="AF3" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AG3" s="1" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="AH3" s="1" t="s">
         <v>23</v>
       </c>
       <c r="AI3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AJ3" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="AJ3" s="1" t="s">
-        <v>45</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="AC2" r:id="rId1"/>
-    <hyperlink ref="AB2" r:id="rId2"/>
-    <hyperlink ref="AB3" r:id="rId3"/>
-    <hyperlink ref="AC3" r:id="rId4"/>
+    <hyperlink ref="AC2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="AB2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="AB3" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="AC3" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId5"/>
